--- a/docs/oc-regiones/licencia-de-software-de-ofimatica/region-de-atacama.xlsx
+++ b/docs/oc-regiones/licencia-de-software-de-ofimatica/region-de-atacama.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M3"/>
+  <dimension ref="A1:M9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -514,7 +514,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>4193-366-CM26</t>
+          <t>4355-207-CM25</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -524,12 +524,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>ago-2026</t>
+          <t>abr-2025</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2025-04-03</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -539,12 +539,12 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>69.030.300-0</t>
+          <t>69.030.600-k</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CALDERA</t>
+          <t>I MUNICIPALIDAD DE FREIRINA</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -554,12 +554,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>SUPER SOFTWARE SPA</t>
+          <t>SEIDOR TECHNOLOGIES S.A.</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>76.486.150-7</t>
+          <t>76.449.580-2</t>
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
@@ -569,13 +569,13 @@
         </is>
       </c>
       <c r="M2" s="2" t="n">
-        <v>53273.68</v>
+        <v>44982</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>751-300-CM26</t>
+          <t>4192-2857-CM25</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -585,27 +585,27 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>ago-2026</t>
+          <t>abr-2025</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2025-04-14</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>72.232.200-2</t>
+          <t>69.030.300-0</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>GOBIERNO REGIONAL DE ATACAMA</t>
+          <t>I MUNICIPALIDAD DE CALDERA</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -615,12 +615,12 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA TELENET LTDA</t>
+          <t>SOFTLINE INTERNATIONAL CHILE SPA</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>77.700.780-7</t>
+          <t>76.232.892-5</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
@@ -630,6 +630,372 @@
         </is>
       </c>
       <c r="M3" s="2" t="n">
+        <v>47113.29</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2923-355-CM25</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>2239-11-LR24</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>jul-2025</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>2025-07-08</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>69.030.100-8</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE CHANARAL</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Región de Atacama </t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>TECNOLOGIA BS SPA</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>76.852.815-2</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="n">
+        <v>10033.07</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>4357-311-CM25</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>2239-11-LR24</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>jul-2025</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>2025-07-29</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>69.030.600-k</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE FREIRINA</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Región de Atacama </t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>TECNOLOGIA BS SPA</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>76.852.815-2</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="n">
+        <v>3848.46</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>4193-395-CM25</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>2239-11-LR24</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>ago-2025</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>2025-08-11</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>69.030.300-0</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE CALDERA</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Región de Atacama </t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>SUPER SOFTWARE SPA</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>76.486.150-7</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="n">
+        <v>28244.41</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>751-1470-CM25</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>2239-11-LR24</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>oct-2025</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>2025-10-16</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>72.232.200-2</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>GOBIERNO REGIONAL DE ATACAMA</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Región de Atacama </t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>COMERCIALIZADORA TELENET LTDA</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>77.700.780-7</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="n">
+        <v>20706</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>4193-366-CM26</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>2239-11-LR24</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>69.030.300-0</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE CALDERA</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Región de Atacama </t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>SUPER SOFTWARE SPA</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>76.486.150-7</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="n">
+        <v>53273.68</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>751-300-CM26</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>2239-11-LR24</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>72.232.200-2</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>GOBIERNO REGIONAL DE ATACAMA</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Región de Atacama </t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>COMERCIALIZADORA TELENET LTDA</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>77.700.780-7</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="n">
         <v>21124.88</v>
       </c>
     </row>
